--- a/rules/CORE-000061/negative/01/data/unit-test-coreid-CG0634-negative.xlsx
+++ b/rules/CORE-000061/negative/01/data/unit-test-coreid-CG0634-negative.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marisa_wyckmans\CORE\CDISC_Rule_Authoring\core-contributor\rules\CORE-000061\negative\01\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{887CBBC0-B1CD-4B03-AC87-626FE225435F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D1E79E6-AAE2-4A9D-979E-F119352C22CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21240" windowHeight="15270" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19310" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
@@ -784,7 +784,7 @@
     <t>2013-01-11</t>
   </si>
   <si>
-    <t>RPLENDY</t>
+    <t>RPPLENDY</t>
   </si>
 </sst>
 </file>
@@ -803,11 +803,13 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -918,7 +920,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1369,7 +1371,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1389,7 +1391,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1409,7 +1411,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
